--- a/Train_A_Skill/Level1_Skill_Horizontal_StraightArmPush_ContraLateralPlankHold.xlsx
+++ b/Train_A_Skill/Level1_Skill_Horizontal_StraightArmPush_ContraLateralPlankHold.xlsx
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -820,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1034,22 +1037,22 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2 Arm Forward Lean Pushup Hold</t>
+          <t>Supinated Shoulder Extension press</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>45s hold, hips in line with shoulders</t>
+          <t>15 reps arms straight with medium intensity band</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>20–45s</t>
+          <t>15 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1061,17 +1064,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Supinated Shoulder Extension press</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>15 reps arms straight with medium intensity band</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>15 reps · light–medium resistance band</t>
+          <t>Full range iron cross press</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1086,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Full range iron cross press</t>
+          <t>Rotational DB Push Hold</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1097,30 +1100,8 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Rotational DB Push Hold</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
@@ -1131,7 +1112,6 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D15:F15"/>
@@ -1149,7 +1129,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1162,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1227,17 +1206,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Weighted Bear Crawl forwards/backwards</t>
+          <t>2 Arm Forward Lean Pushup Hold</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>60s nonstop at 30% bodyweight</t>
+          <t>45s hold, hips in line with shoulders</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>45–60s @ 20–30% BW</t>
+          <t>20–45s</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1228,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>High Lizard Crawl</t>
+          <t>Weighted Bear Crawl forwards/backwards</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>90s nonstop</t>
+          <t>60s nonstop at 30% bodyweight</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>45–90s</t>
+          <t>45–60s @ 20–30% BW</t>
         </is>
       </c>
     </row>
@@ -1271,17 +1250,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Rotational High Lizard Crawl</t>
+          <t>High Lizard Crawl</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>60s nonstop</t>
+          <t>90s nonstop</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>30–60s</t>
+          <t>45–90s</t>
         </is>
       </c>
     </row>
@@ -1293,17 +1272,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Single arm bear scapula push-ups</t>
+          <t>Rotational High Lizard Crawl</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>10 reps each arm, hips in line w/ shoulders</t>
+          <t>60s nonstop</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>30–60s</t>
         </is>
       </c>
     </row>
@@ -1315,17 +1294,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>horizontal support hold scapula push-ups + holds</t>
+          <t>Single arm bear scapula push-ups</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>20 reps + 60s hold (horizontal)</t>
+          <t>10 reps each arm, hips in line w/ shoulders</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>10–20 reps · rest · 15–60s hold</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -1337,17 +1316,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Assisted SA Scapula Push-up</t>
+          <t>horizontal support hold scapula push-ups + holds</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>12 reps each side</t>
+          <t>20 reps + 60s hold (horizontal)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>6–12 reps</t>
+          <t>10–20 reps · rest · 15–60s hold</t>
         </is>
       </c>
     </row>
@@ -1359,105 +1338,105 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
+          <t>Assisted SA Scapula Push-up</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>12 reps each side</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>6–12 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
           <t>Single arm plank hold</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>60s hold, hips in line with shoulders</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>30–60s</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Contra-lateral Bear Scapula pushups</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>10 push-ups each side + 30s hold each side</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>6–10 reps/side · rest · 10–30s hold/side</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Single arm scapula pushups</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>10 reps each side, hips square</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>6–10 reps</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Horizontal supinated support hold rings</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Supinated Shoulder Extension press</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>15 reps arms straight with medium intensity band</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>15 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1469,17 +1448,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Full range iron cross press</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+          <t>Supinated Shoulder Extension press</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>15 reps arms straight with medium intensity band</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>15 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1491,40 +1470,63 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>Full range iron cross press</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
           <t>Rotational DB Push Hold</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D19:F19"/>
+  <mergeCells count="19">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
@@ -1540,6 +1542,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1603,22 +1606,22 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>TEST: Contra-lateral Plank Hold</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>PASS: 30s hold each side</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>10–30s each side · 2 sets</t>
         </is>
